--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>7.416025037515808</v>
+        <v>1.205104068596319</v>
       </c>
       <c r="D2" t="n">
-        <v>8.933975170224246</v>
+        <v>1.45177096516144</v>
       </c>
       <c r="E2" t="n">
-        <v>5.398727076300373</v>
+        <v>0.8772931498988106</v>
       </c>
       <c r="F2" t="n">
-        <v>4.056352009526619</v>
+        <v>0.6591572015480757</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>18.73517451925872</v>
+        <v>3.044465859379542</v>
       </c>
       <c r="D3" t="n">
-        <v>19.22077401228623</v>
+        <v>3.123375776996512</v>
       </c>
       <c r="E3" t="n">
-        <v>5.398727076300373</v>
+        <v>0.8772931498988106</v>
       </c>
       <c r="F3" t="n">
-        <v>4.056352009526619</v>
+        <v>0.6591572015480757</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>18.84893833388813</v>
+        <v>3.062952479256821</v>
       </c>
       <c r="D4" t="n">
-        <v>18.47740571272584</v>
+        <v>3.00257842831795</v>
       </c>
       <c r="E4" t="n">
-        <v>5.398727076300373</v>
+        <v>0.8772931498988106</v>
       </c>
       <c r="F4" t="n">
-        <v>4.056352009526619</v>
+        <v>0.6591572015480757</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.643685897722749</v>
+        <v>1.404598958379947</v>
       </c>
       <c r="D5" t="n">
-        <v>15.54240011442512</v>
+        <v>2.525640018594081</v>
       </c>
       <c r="E5" t="n">
-        <v>5.398727076300373</v>
+        <v>0.8772931498988106</v>
       </c>
       <c r="F5" t="n">
-        <v>4.056352009526619</v>
+        <v>0.6591572015480757</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
